--- a/data/trans_orig/P22$ss-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P22$ss-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>997092</t>
+          <t>997522</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1015533</t>
+          <t>1016472</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1259493</t>
+          <t>1256458</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1284181</t>
+          <t>1283772</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2265324</t>
+          <t>2265230</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2297637</t>
+          <t>2296294</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,0%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9163</t>
+          <t>9426</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25649</t>
+          <t>24949</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19212</t>
+          <t>19423</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40675</t>
+          <t>41384</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31933</t>
+          <t>32351</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>58069</t>
+          <t>59071</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8781</t>
+          <t>9141</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25576</t>
+          <t>26816</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8414</t>
+          <t>8538</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25043</t>
+          <t>24036</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>21672</t>
+          <t>21291</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>43141</t>
+          <t>44183</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4242</t>
+          <t>3574</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16484</t>
+          <t>15721</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15066</t>
+          <t>14274</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32735</t>
+          <t>32394</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21816</t>
+          <t>21513</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44692</t>
+          <t>42613</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8204</t>
+          <t>8369</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24754</t>
+          <t>23211</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6125</t>
+          <t>6818</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9653</t>
+          <t>9758</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>26121</t>
+          <t>26158</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13000</t>
+          <t>12542</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5601</t>
+          <t>4647</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1652</t>
+          <t>1645</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12910</t>
+          <t>13703</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8630</t>
+          <t>8608</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8675</t>
+          <t>7752</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,33%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1621171</t>
+          <t>1622141</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1651680</t>
+          <t>1652043</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1506369</t>
+          <t>1505968</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1538464</t>
+          <t>1538176</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3139273</t>
+          <t>3139459</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3182450</t>
+          <t>3182824</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,15%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34475</t>
+          <t>34487</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>62144</t>
+          <t>61772</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>37902</t>
+          <t>38416</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>66542</t>
+          <t>67770</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>78248</t>
+          <t>77460</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>117370</t>
+          <t>118471</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23267</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48132</t>
+          <t>46753</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19349</t>
+          <t>20750</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42545</t>
+          <t>42435</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>48638</t>
+          <t>48483</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>81839</t>
+          <t>81931</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19513</t>
+          <t>20179</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42171</t>
+          <t>41544</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>46544</t>
+          <t>47000</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>80679</t>
+          <t>78777</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>72109</t>
+          <t>73801</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>112515</t>
+          <t>111921</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30690</t>
+          <t>30863</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>56731</t>
+          <t>57654</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2015,12 +2015,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2819</t>
+          <t>2309</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14647</t>
+          <t>13491</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2030,12 +2030,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2050,12 +2050,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>36016</t>
+          <t>37046</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>64150</t>
+          <t>64768</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2065,12 +2065,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8865</t>
+          <t>11581</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6957</t>
+          <t>4960</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9849</t>
+          <t>9168</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8182</t>
+          <t>9532</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,12 +2241,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>741</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9882</t>
+          <t>9845</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2276,12 +2276,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1499</t>
+          <t>1695</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11844</t>
+          <t>14623</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,45%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>467191</t>
+          <t>467399</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>498479</t>
+          <t>497194</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>412455</t>
+          <t>413127</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>438432</t>
+          <t>439709</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>886634</t>
+          <t>889338</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>930011</t>
+          <t>930645</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,55%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>41377</t>
+          <t>42064</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>70690</t>
+          <t>70842</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23520</t>
+          <t>23556</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>47334</t>
+          <t>46925</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>72540</t>
+          <t>71102</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>109226</t>
+          <t>107636</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13358</t>
+          <t>13055</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>32095</t>
+          <t>31242</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>16210</t>
+          <t>16268</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>36740</t>
+          <t>36778</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>33365</t>
+          <t>33916</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>61834</t>
+          <t>59548</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -2662,12 +2662,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>40998</t>
+          <t>40544</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>69723</t>
+          <t>69024</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2677,12 +2677,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>36731</t>
+          <t>36564</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>64513</t>
+          <t>63137</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,12 +2732,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>85660</t>
+          <t>83419</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>122695</t>
+          <t>123932</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,06%</t>
         </is>
       </c>
     </row>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9380</t>
+          <t>9525</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26647</t>
+          <t>26120</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,12 +2810,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5047</t>
+          <t>4952</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18433</t>
+          <t>17281</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18560</t>
+          <t>17413</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>39756</t>
+          <t>37457</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8426</t>
+          <t>8011</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9874</t>
+          <t>9408</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>984</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11809</t>
+          <t>11085</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3086,12 +3086,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3107381</t>
+          <t>3106908</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3153465</t>
+          <t>3151417</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3197097</t>
+          <t>3198295</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3246151</t>
+          <t>3247317</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6315493</t>
+          <t>6317930</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6383131</t>
+          <t>6390272</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,13%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>97585</t>
+          <t>96485</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>139614</t>
+          <t>139565</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,82 +3246,82 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>2,95%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>4,27%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>113471</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>92490</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>134696</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>3,36%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>3,99%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>230564</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>198013</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>261137</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>3,47%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>2,98%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>4,27%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>113471</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>92763</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>135492</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>3,36%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>2,75%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>4,01%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>230564</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>201647</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>263294</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>3,03%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -3344,12 +3344,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>54737</t>
+          <t>55000</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>89218</t>
+          <t>88610</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3359,12 +3359,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>53667</t>
+          <t>57167</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>87804</t>
+          <t>90229</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3394,12 +3394,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>115980</t>
+          <t>118130</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>162688</t>
+          <t>166093</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3429,12 +3429,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -3457,12 +3457,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>74314</t>
+          <t>74994</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>112315</t>
+          <t>111322</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3472,12 +3472,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>110901</t>
+          <t>111302</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>158730</t>
+          <t>156032</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3507,12 +3507,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>197272</t>
+          <t>197741</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>256187</t>
+          <t>255619</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,12 +3570,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>57796</t>
+          <t>57515</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>91154</t>
+          <t>93141</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3585,12 +3585,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>11325</t>
+          <t>10797</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>29491</t>
+          <t>28701</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3620,12 +3620,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>73991</t>
+          <t>73090</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>113186</t>
+          <t>113063</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3683,12 +3683,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1659</t>
+          <t>1656</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>15454</t>
+          <t>15998</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6450</t>
+          <t>7014</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,12 +3753,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3139</t>
+          <t>2864</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>16800</t>
+          <t>17250</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>11118</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,12 +3831,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3513</t>
+          <t>4019</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>16589</t>
+          <t>18568</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,12 +3866,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>5570</t>
+          <t>5643</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>21446</t>
+          <t>21739</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>947717</t>
+          <t>949889</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>965921</t>
+          <t>965821</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4159,49 +4159,49 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>99,09%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1229</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1317777</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1306880</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>1325841</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>98,5%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>97,69%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
           <t>99,11%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1229</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1317777</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1306330</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1325719</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>98,5%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>97,65%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>99,1%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2123</t>
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2264026</t>
+          <t>2263132</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2288715</t>
+          <t>2288037</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2828</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12739</t>
+          <t>11733</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9249</t>
+          <t>10261</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25893</t>
+          <t>26489</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14133</t>
+          <t>14188</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32614</t>
+          <t>33970</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12742</t>
+          <t>13298</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4036</t>
+          <t>4110</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19206</t>
+          <t>18170</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>7844</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>23997</t>
+          <t>24256</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3713</t>
+          <t>3789</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15562</t>
+          <t>15534</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9991</t>
+          <t>9795</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28444</t>
+          <t>27612</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16351</t>
+          <t>16034</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36590</t>
+          <t>37506</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -4596,12 +4596,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>800</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7918</t>
+          <t>7516</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5372</t>
+          <t>4359</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>982</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9662</t>
+          <t>8842</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7591</t>
+          <t>6846</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4784,7 +4784,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>10668</t>
+          <t>6940</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,3%</t>
         </is>
       </c>
     </row>
@@ -4827,7 +4827,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4899</t>
+          <t>3652</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1044</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10478</t>
+          <t>9562</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1862</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10767</t>
+          <t>11791</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1861706</t>
+          <t>1860825</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1901351</t>
+          <t>1899516</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1674012</t>
+          <t>1674023</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1709786</t>
+          <t>1709056</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3544838</t>
+          <t>3547128</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3600428</t>
+          <t>3599953</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,75%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>33795</t>
+          <t>34258</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>62605</t>
+          <t>61954</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23868</t>
+          <t>23386</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46196</t>
+          <t>46933</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>64799</t>
+          <t>64463</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>102568</t>
+          <t>99940</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -5165,12 +5165,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34853</t>
+          <t>34845</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65913</t>
+          <t>65099</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18586</t>
+          <t>19125</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42750</t>
+          <t>44047</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5215,12 +5215,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>60292</t>
+          <t>59627</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>98352</t>
+          <t>98720</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5250,12 +5250,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -5278,12 +5278,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>41956</t>
+          <t>42319</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>74929</t>
+          <t>77366</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5293,12 +5293,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>50896</t>
+          <t>51036</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>88102</t>
+          <t>85675</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>100002</t>
+          <t>100853</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>151493</t>
+          <t>148784</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -5391,12 +5391,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18581</t>
+          <t>19031</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>41741</t>
+          <t>41305</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5406,12 +5406,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9843</t>
+          <t>9961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>21744</t>
+          <t>21986</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>45030</t>
+          <t>46375</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -5509,7 +5509,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5255</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7182</t>
+          <t>6740</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9692</t>
+          <t>8552</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,23%</t>
         </is>
       </c>
     </row>
@@ -5652,12 +5652,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10585</t>
+          <t>11007</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10375</t>
+          <t>10626</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5707,7 +5707,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
     </row>
@@ -5734,12 +5734,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>395476</t>
+          <t>394183</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>430026</t>
+          <t>429212</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>396633</t>
+          <t>396849</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>424426</t>
+          <t>425650</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>801339</t>
+          <t>804602</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>848323</t>
+          <t>848327</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -5847,12 +5847,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26242</t>
+          <t>25569</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>51362</t>
+          <t>51523</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5862,12 +5862,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15164</t>
+          <t>15376</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36970</t>
+          <t>37478</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>44867</t>
+          <t>46458</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>80324</t>
+          <t>78364</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -5960,12 +5960,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14429</t>
+          <t>13978</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>36894</t>
+          <t>36838</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5975,12 +5975,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5995,12 +5995,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>18713</t>
+          <t>17802</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>42716</t>
+          <t>41607</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6010,12 +6010,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>37765</t>
+          <t>37816</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>69328</t>
+          <t>69214</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -6073,12 +6073,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>34655</t>
+          <t>35544</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>64453</t>
+          <t>66349</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6108,12 +6108,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>25567</t>
+          <t>24926</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>49187</t>
+          <t>48717</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>64117</t>
+          <t>63168</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>102813</t>
+          <t>100675</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3203</t>
+          <t>3077</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17981</t>
+          <t>16587</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3888</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15946</t>
+          <t>15477</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8921</t>
+          <t>8965</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>26313</t>
+          <t>26772</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6936</t>
+          <t>6088</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6319,7 +6319,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6374,7 +6374,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6027</t>
+          <t>4876</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -6452,7 +6452,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11421</t>
+          <t>10030</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6467,7 +6467,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6487,7 +6487,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10677</t>
+          <t>12111</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6502,7 +6502,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -6529,12 +6529,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3227396</t>
+          <t>3227565</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3284408</t>
+          <t>3282456</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6564,12 +6564,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3396556</t>
+          <t>3398247</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3446242</t>
+          <t>3444752</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6579,12 +6579,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6599,12 +6599,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6642488</t>
+          <t>6644646</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6716043</t>
+          <t>6718066</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6614,12 +6614,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,34%</t>
         </is>
       </c>
     </row>
@@ -6642,12 +6642,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>70165</t>
+          <t>71275</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>112993</t>
+          <t>110524</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6657,12 +6657,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6677,12 +6677,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>57410</t>
+          <t>58212</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>94810</t>
+          <t>93881</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6712,12 +6712,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>138251</t>
+          <t>138230</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>191725</t>
+          <t>192658</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6732,7 +6732,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -6755,12 +6755,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>59320</t>
+          <t>59473</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>95835</t>
+          <t>95619</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6790,12 +6790,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>48831</t>
+          <t>50951</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>88026</t>
+          <t>88039</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6805,7 +6805,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -6825,12 +6825,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>117070</t>
+          <t>118557</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>170972</t>
+          <t>168027</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -6868,12 +6868,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>92531</t>
+          <t>91916</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>137951</t>
+          <t>138585</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>98826</t>
+          <t>98284</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>142128</t>
+          <t>146292</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6938,12 +6938,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>198515</t>
+          <t>200313</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>265599</t>
+          <t>264821</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -6981,12 +6981,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>26529</t>
+          <t>26305</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>52200</t>
+          <t>54027</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7016,12 +7016,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6993</t>
+          <t>7265</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>20250</t>
+          <t>21656</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7051,12 +7051,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>38135</t>
+          <t>38921</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>69072</t>
+          <t>67710</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -7094,12 +7094,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1211</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>9940</t>
+          <t>9947</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7134,7 +7134,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>5186</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7164,12 +7164,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>12300</t>
+          <t>12613</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4687</t>
+          <t>4123</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7227,7 +7227,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7242,12 +7242,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>5455</t>
+          <t>6040</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>20444</t>
+          <t>22005</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7257,12 +7257,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7277,12 +7277,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>5872</t>
+          <t>6692</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>20569</t>
+          <t>22524</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7292,12 +7292,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,32%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>735975</t>
+          <t>736760</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>748526</t>
+          <t>749226</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>970493</t>
+          <t>972192</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>985925</t>
+          <t>985773</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1712992</t>
+          <t>1713988</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1731771</t>
+          <t>1732651</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -7668,12 +7668,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3995</t>
+          <t>3125</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16491</t>
+          <t>15310</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7683,12 +7683,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7703,12 +7703,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11006</t>
+          <t>10307</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6549</t>
+          <t>6452</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20651</t>
+          <t>21829</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7354</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7816,12 +7816,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11494</t>
+          <t>10524</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7831,12 +7831,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7851,12 +7851,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2405</t>
+          <t>2563</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13362</t>
+          <t>14169</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -7894,12 +7894,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12045</t>
+          <t>11266</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7929,12 +7929,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4841</t>
+          <t>5154</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19497</t>
+          <t>20587</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7944,47 +7944,47 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>15375</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>8626</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>26596</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>0,49%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>15375</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>8607</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>26166</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -8047,7 +8047,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4272</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8082,7 +8082,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4431</t>
+          <t>3556</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8097,7 +8097,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,2%</t>
         </is>
       </c>
     </row>
@@ -8350,12 +8350,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1977743</t>
+          <t>1977489</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2014372</t>
+          <t>2015540</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8365,12 +8365,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8385,12 +8385,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1917139</t>
+          <t>1919328</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1948379</t>
+          <t>1948361</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8420,12 +8420,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3905326</t>
+          <t>3908305</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3953805</t>
+          <t>3953559</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8435,7 +8435,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8463,12 +8463,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26343</t>
+          <t>27035</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>52057</t>
+          <t>51388</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8498,12 +8498,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9052</t>
+          <t>9132</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25905</t>
+          <t>26309</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8518,7 +8518,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8533,12 +8533,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>41890</t>
+          <t>41914</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>70904</t>
+          <t>70942</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21989</t>
+          <t>22687</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46864</t>
+          <t>47014</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8611,12 +8611,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12770</t>
+          <t>13255</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34079</t>
+          <t>33185</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8646,12 +8646,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39772</t>
+          <t>40390</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70608</t>
+          <t>73239</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -8689,12 +8689,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>35978</t>
+          <t>34995</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>66287</t>
+          <t>63960</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8704,12 +8704,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8724,12 +8724,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>52155</t>
+          <t>52760</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>84693</t>
+          <t>84433</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8739,12 +8739,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8759,12 +8759,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>97374</t>
+          <t>95918</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>140764</t>
+          <t>139279</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4430</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19908</t>
+          <t>19727</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8817,12 +8817,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8837,12 +8837,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2844</t>
+          <t>2044</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13209</t>
+          <t>12747</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8852,12 +8852,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8872,12 +8872,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>9259</t>
+          <t>9373</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>26646</t>
+          <t>28622</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8892,7 +8892,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -8915,12 +8915,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13302</t>
+          <t>15665</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8950,12 +8950,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>851</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8320</t>
+          <t>8908</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8970,42 +8970,42 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>7474</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>2909</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>16948</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
           <t>0,42%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>7474</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>3132</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>16489</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
         </is>
       </c>
     </row>
@@ -9033,7 +9033,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6794</t>
+          <t>7038</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9048,7 +9048,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9102</t>
+          <t>8719</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9083,7 +9083,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9098,12 +9098,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>981</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12117</t>
+          <t>10538</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9113,12 +9113,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,26%</t>
         </is>
       </c>
     </row>
@@ -9145,12 +9145,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>447737</t>
+          <t>447766</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>481742</t>
+          <t>483035</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9160,12 +9160,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9180,12 +9180,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>470157</t>
+          <t>471196</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>501410</t>
+          <t>501200</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9195,12 +9195,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9215,12 +9215,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>928936</t>
+          <t>929007</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>975399</t>
+          <t>975857</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,11%</t>
         </is>
       </c>
     </row>
@@ -9258,12 +9258,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21473</t>
+          <t>21719</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>43318</t>
+          <t>42916</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9273,12 +9273,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9293,12 +9293,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16404</t>
+          <t>16486</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>38077</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9308,12 +9308,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9328,12 +9328,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>43099</t>
+          <t>42937</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>72827</t>
+          <t>72493</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9343,12 +9343,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -9371,12 +9371,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>25330</t>
+          <t>25436</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>51279</t>
+          <t>49707</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9386,12 +9386,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9406,12 +9406,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>23226</t>
+          <t>23912</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>45487</t>
+          <t>45820</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9421,12 +9421,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9441,12 +9441,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>52897</t>
+          <t>54194</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>87040</t>
+          <t>85129</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9456,12 +9456,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -9484,12 +9484,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>45202</t>
+          <t>44633</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>74613</t>
+          <t>73998</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9499,12 +9499,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9519,12 +9519,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>61749</t>
+          <t>64450</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>97156</t>
+          <t>95928</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9534,12 +9534,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9554,12 +9554,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>115663</t>
+          <t>116955</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>160756</t>
+          <t>161192</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9569,12 +9569,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,72%</t>
         </is>
       </c>
     </row>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3131</t>
+          <t>3504</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16801</t>
+          <t>17334</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9612,12 +9612,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9632,12 +9632,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>2557</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12594</t>
+          <t>12451</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9647,12 +9647,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9667,12 +9667,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8266</t>
+          <t>8232</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24591</t>
+          <t>24485</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9687,7 +9687,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7677</t>
+          <t>8592</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9730,7 +9730,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>8779</t>
+          <t>7424</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -9828,7 +9828,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5846</t>
+          <t>5866</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9863,7 +9863,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5652</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9878,7 +9878,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9898,7 +9898,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6844</t>
+          <t>7518</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9913,7 +9913,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -9940,12 +9940,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3182211</t>
+          <t>3180355</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3234759</t>
+          <t>3233473</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9955,12 +9955,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9975,12 +9975,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3377150</t>
+          <t>3376285</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3423330</t>
+          <t>3424508</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9990,12 +9990,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10010,12 +10010,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6573434</t>
+          <t>6573534</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6642594</t>
+          <t>6640102</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,25%</t>
         </is>
       </c>
     </row>
@@ -10053,12 +10053,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>60756</t>
+          <t>59934</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>96829</t>
+          <t>97362</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10068,12 +10068,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10088,12 +10088,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>33304</t>
+          <t>33767</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>61171</t>
+          <t>61264</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10103,12 +10103,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>101630</t>
+          <t>102607</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>146355</t>
+          <t>148335</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -10166,12 +10166,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>53156</t>
+          <t>55333</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>90118</t>
+          <t>91305</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10181,12 +10181,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>45793</t>
+          <t>43578</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>76045</t>
+          <t>77642</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10216,12 +10216,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -10236,12 +10236,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>106281</t>
+          <t>107083</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>155511</t>
+          <t>152878</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -10279,12 +10279,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>91322</t>
+          <t>91625</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>135306</t>
+          <t>134786</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10294,12 +10294,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10314,12 +10314,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>131660</t>
+          <t>131027</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>182052</t>
+          <t>184847</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10329,12 +10329,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10349,12 +10349,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>237726</t>
+          <t>236314</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>304725</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10364,12 +10364,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10973</t>
+          <t>11206</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>32699</t>
+          <t>30682</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10412,7 +10412,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10427,12 +10427,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6936</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>21514</t>
+          <t>20674</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10447,7 +10447,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10462,12 +10462,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>21325</t>
+          <t>22079</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>46563</t>
+          <t>47519</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10477,12 +10477,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -10505,12 +10505,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2276</t>
+          <t>2446</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>15623</t>
+          <t>16165</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10525,7 +10525,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10540,12 +10540,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>846</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>9300</t>
+          <t>8731</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10560,7 +10560,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10575,12 +10575,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4538</t>
+          <t>4221</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>18934</t>
+          <t>19012</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10590,12 +10590,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
     </row>
@@ -10618,12 +10618,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>951</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9338</t>
+          <t>8780</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10638,7 +10638,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>10535</t>
+          <t>11110</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10673,7 +10673,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2394</t>
+          <t>2602</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>13867</t>
+          <t>15019</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10703,12 +10703,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
     </row>
@@ -10961,32 +10961,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>510320</t>
+          <t>573278</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>504722</t>
+          <t>567037</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>513252</t>
+          <t>576582</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10996,32 +10996,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>745809</t>
+          <t>812983</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>740051</t>
+          <t>806569</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>749005</t>
+          <t>816394</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11031,32 +11031,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1256130</t>
+          <t>1386262</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1249718</t>
+          <t>1378040</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1261143</t>
+          <t>1391253</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -11074,7 +11074,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -11084,7 +11084,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3987</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11099,7 +11099,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11109,17 +11109,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>671</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>5860</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11129,12 +11129,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11144,17 +11144,17 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>2954</t>
+          <t>3277</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1146</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6101</t>
+          <t>7472</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11164,12 +11164,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -11187,7 +11187,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>477</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -11197,12 +11197,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2380</t>
+          <t>2405</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -11212,7 +11212,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11222,32 +11222,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4235</t>
+          <t>4422</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9030</t>
+          <t>9200</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11257,32 +11257,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2221</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9231</t>
+          <t>9964</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -11300,32 +11300,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9778</t>
+          <t>10278</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5215</t>
+          <t>5126</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17201</t>
+          <t>17674</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11335,32 +11335,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13675</t>
+          <t>14302</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8716</t>
+          <t>8895</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21947</t>
+          <t>21349</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11370,32 +11370,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>23454</t>
+          <t>24580</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16531</t>
+          <t>17132</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33501</t>
+          <t>34696</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -11413,7 +11413,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>998</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>5985</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -11438,7 +11438,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>431</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -11458,7 +11458,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1823</t>
+          <t>2185</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11483,7 +11483,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>1429</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -11493,12 +11493,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7294</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -11508,7 +11508,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -11526,7 +11526,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1691</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5819</t>
+          <t>7628</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11561,7 +11561,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>4645</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -11586,7 +11586,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11596,32 +11596,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2831</t>
+          <t>3256</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>914</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6573</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -11674,7 +11674,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>1213</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -11684,12 +11684,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3703</t>
+          <t>3892</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11709,7 +11709,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>1213</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -11719,12 +11719,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>4070</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -11734,7 +11734,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,29%</t>
         </is>
       </c>
     </row>
@@ -11756,32 +11756,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2223527</t>
+          <t>2156682</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2199707</t>
+          <t>2134091</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2245441</t>
+          <t>2174926</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11791,32 +11791,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2195694</t>
+          <t>2124845</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2179580</t>
+          <t>2109263</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2207726</t>
+          <t>2135223</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11826,32 +11826,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4419221</t>
+          <t>4281527</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4392962</t>
+          <t>4254887</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4446000</t>
+          <t>4302186</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>97,76%</t>
         </is>
       </c>
     </row>
@@ -11869,32 +11869,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>56715</t>
+          <t>55884</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>37502</t>
+          <t>40883</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>77894</t>
+          <t>72795</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11904,32 +11904,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>19139</t>
+          <t>20338</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12342</t>
+          <t>14275</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27530</t>
+          <t>28065</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11939,32 +11939,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>75854</t>
+          <t>76222</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>55848</t>
+          <t>58729</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>98120</t>
+          <t>95827</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -11982,32 +11982,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>52481</t>
+          <t>55869</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34156</t>
+          <t>39728</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74580</t>
+          <t>77282</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12017,32 +12017,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31238</t>
+          <t>33238</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20716</t>
+          <t>25031</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44121</t>
+          <t>45949</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12052,32 +12052,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>83719</t>
+          <t>89107</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>62157</t>
+          <t>70299</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>109573</t>
+          <t>113190</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -12095,32 +12095,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>95219</t>
+          <t>106188</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>65945</t>
+          <t>84964</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>122531</t>
+          <t>128837</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12130,32 +12130,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>135376</t>
+          <t>153097</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>95289</t>
+          <t>132835</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>162330</t>
+          <t>175834</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12165,32 +12165,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>230595</t>
+          <t>259286</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>184855</t>
+          <t>229106</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>270988</t>
+          <t>292837</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -12208,27 +12208,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28647</t>
+          <t>29803</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18026</t>
+          <t>19369</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>45970</t>
+          <t>44739</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -12243,32 +12243,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11041</t>
+          <t>11551</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6392</t>
+          <t>7161</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>18048</t>
+          <t>18960</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -12278,32 +12278,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>39688</t>
+          <t>41353</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>27909</t>
+          <t>30287</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>58454</t>
+          <t>57749</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -12321,7 +12321,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1177</t>
+          <t>2966</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -12331,12 +12331,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5092</t>
+          <t>10776</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -12346,7 +12346,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12356,67 +12356,67 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4854</t>
+          <t>5355</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2044</t>
+          <t>2289</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11178</t>
+          <t>10806</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>8321</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>4099</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>16899</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>0,09%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>6032</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>2411</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>11283</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,05%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -12434,22 +12434,22 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4193</t>
+          <t>4230</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1206</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12450</t>
+          <t>12541</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -12459,7 +12459,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12469,32 +12469,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7389</t>
+          <t>9243</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2871</t>
+          <t>4157</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19040</t>
+          <t>22112</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12504,32 +12504,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>11582</t>
+          <t>13473</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5694</t>
+          <t>6768</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>26836</t>
+          <t>26490</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -12551,32 +12551,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>599090</t>
+          <t>656153</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>584547</t>
+          <t>640591</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>610490</t>
+          <t>669380</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12586,32 +12586,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>603906</t>
+          <t>675110</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>591358</t>
+          <t>660701</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>615043</t>
+          <t>686724</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12621,17 +12621,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1202996</t>
+          <t>1331264</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1183743</t>
+          <t>1311291</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1219968</t>
+          <t>1348985</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12641,12 +12641,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,26%</t>
         </is>
       </c>
     </row>
@@ -12664,32 +12664,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>33329</t>
+          <t>35492</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23141</t>
+          <t>24631</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>46301</t>
+          <t>48503</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12699,32 +12699,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>39029</t>
+          <t>41501</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30742</t>
+          <t>32823</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49922</t>
+          <t>52665</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12734,32 +12734,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>72358</t>
+          <t>76993</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>59159</t>
+          <t>61685</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>87850</t>
+          <t>92627</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -12777,32 +12777,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>39415</t>
+          <t>46279</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>28008</t>
+          <t>34089</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>52582</t>
+          <t>61878</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12812,32 +12812,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>52810</t>
+          <t>56600</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>42000</t>
+          <t>44108</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>66871</t>
+          <t>71499</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12847,32 +12847,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>92225</t>
+          <t>102879</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>76357</t>
+          <t>84740</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>111160</t>
+          <t>123489</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -12890,32 +12890,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>102361</t>
+          <t>115680</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>86109</t>
+          <t>96223</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>122750</t>
+          <t>138994</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12925,32 +12925,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>131709</t>
+          <t>146000</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>114510</t>
+          <t>127668</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>150524</t>
+          <t>166344</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -12960,32 +12960,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>234070</t>
+          <t>261680</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>209592</t>
+          <t>233757</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>261495</t>
+          <t>289177</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,99%</t>
         </is>
       </c>
     </row>
@@ -13003,32 +13003,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>17882</t>
+          <t>20573</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10542</t>
+          <t>12502</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30666</t>
+          <t>32940</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13038,32 +13038,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>12107</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5967</t>
+          <t>6858</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19140</t>
+          <t>20503</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13073,32 +13073,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>29051</t>
+          <t>32679</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19857</t>
+          <t>22593</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>41644</t>
+          <t>47884</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -13229,32 +13229,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4833</t>
+          <t>4788</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>1377</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11630</t>
+          <t>14509</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13264,22 +13264,22 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>405</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6180</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -13289,7 +13289,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13299,32 +13299,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6858</t>
+          <t>6809</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2715</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>14249</t>
+          <t>14842</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -13346,69 +13346,69 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>3332938</t>
+          <t>3386114</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3304774</t>
+          <t>3357406</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3361736</t>
+          <t>3408982</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>96,83%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>5183</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>3612939</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>3592560</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3629348</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>96,95%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>96,41%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
           <t>97,39%</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>5183</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>3545409</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>3523591</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>3565463</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>97,1%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>96,5%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>97,65%</t>
-        </is>
-      </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>8418</t>
@@ -13416,32 +13416,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>6878347</t>
+          <t>6999052</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6839687</t>
+          <t>6965212</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6911260</t>
+          <t>7027870</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>96,97%</t>
         </is>
       </c>
     </row>
@@ -13459,32 +13459,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>91149</t>
+          <t>92585</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>67558</t>
+          <t>74262</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>116083</t>
+          <t>113984</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13494,32 +13494,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>60018</t>
+          <t>63906</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>45807</t>
+          <t>52981</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>73159</t>
+          <t>76241</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13529,32 +13529,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>151167</t>
+          <t>156491</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>123896</t>
+          <t>134859</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>181749</t>
+          <t>181497</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -13572,32 +13572,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>92361</t>
+          <t>102625</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>69537</t>
+          <t>82987</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>117775</t>
+          <t>130768</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -13607,32 +13607,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>88283</t>
+          <t>94261</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>70133</t>
+          <t>77567</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>109175</t>
+          <t>113575</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -13642,32 +13642,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>180644</t>
+          <t>196886</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>148520</t>
+          <t>172335</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>213200</t>
+          <t>229544</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -13685,32 +13685,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>207358</t>
+          <t>232146</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>160950</t>
+          <t>202267</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>240599</t>
+          <t>270297</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13720,32 +13720,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>280760</t>
+          <t>313400</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>232627</t>
+          <t>283837</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>316351</t>
+          <t>344564</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13755,32 +13755,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>488118</t>
+          <t>545545</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>420062</t>
+          <t>502728</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>540977</t>
+          <t>586688</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -13798,32 +13798,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>47582</t>
+          <t>51374</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>32775</t>
+          <t>37109</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>65000</t>
+          <t>70059</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13833,32 +13833,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>22614</t>
+          <t>24088</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>15042</t>
+          <t>16817</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>32347</t>
+          <t>34106</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13868,32 +13868,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>70196</t>
+          <t>75462</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>53224</t>
+          <t>59468</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>89372</t>
+          <t>97033</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -13911,22 +13911,22 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2868</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>883</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>7746</t>
+          <t>12570</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -13936,7 +13936,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13946,67 +13946,67 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>5995</t>
+          <t>6660</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2963</t>
+          <t>2792</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>11773</t>
+          <t>11977</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>11577</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>6424</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>19729</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
           <t>0,16%</t>
         </is>
       </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>8863</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>4716</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>15514</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,27%</t>
         </is>
       </c>
     </row>
@@ -14024,17 +14024,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>9026</t>
+          <t>9018</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3636</t>
+          <t>3904</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>18034</t>
+          <t>17912</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14059,32 +14059,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>10168</t>
+          <t>12477</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>5066</t>
+          <t>6952</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>24226</t>
+          <t>25894</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14094,27 +14094,27 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>19194</t>
+          <t>21495</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>11796</t>
+          <t>12703</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>35616</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
